--- a/templates/exodouxoi.xlsx
+++ b/templates/exodouxoi.xlsx
@@ -2670,7 +2670,7 @@
     <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="45" fitToWidth="0"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="45"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
